--- a/data/inventories_ei310.xlsx
+++ b/data/inventories_ei310.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE71538-D7F7-452E-B840-C04FAB8DE3ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11179947-0382-4CF6-9706-C59C2E9AA66F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="hydrogen" sheetId="14" r:id="rId1"/>
     <sheet name="ammonia" sheetId="15" r:id="rId2"/>
     <sheet name="nitrous_oxide" sheetId="25" r:id="rId3"/>
+    <sheet name="hydrogen_peroxide" sheetId="26" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="125">
   <si>
     <t>Activity</t>
   </si>
@@ -335,9 +336,6 @@
     <t>Nitrogen</t>
   </si>
   <si>
-    <t>Oxygen</t>
-  </si>
-  <si>
     <t>ecoinvent-3.10-biosphere</t>
   </si>
   <si>
@@ -347,9 +345,6 @@
     <t>hydrogen production, PEM electrolysis, green</t>
   </si>
   <si>
-    <t>ecoinvent-nc-3.10-cutoff-image-SSP2-Base-2020</t>
-  </si>
-  <si>
     <t>nitrous-oxide-ei310-Base-2020</t>
   </si>
   <si>
@@ -362,25 +357,52 @@
     <t>ammonia, anhydrous, liquid</t>
   </si>
   <si>
-    <t>Nitric acid</t>
-  </si>
-  <si>
-    <t>nitrous oxide production, BAU, fossil ammonia</t>
-  </si>
-  <si>
-    <t>nitrous oxide production, BAU, green ammonia</t>
-  </si>
-  <si>
-    <t>nitrous oxide production, AON, fossil ammonia</t>
-  </si>
-  <si>
-    <t>nitrous oxide production, AON, green ammonia</t>
-  </si>
-  <si>
     <t>nitrous oxide production, AON ideal, fossil ammonia</t>
   </si>
   <si>
     <t>nitrous oxide production, AON ideal, green ammonia</t>
+  </si>
+  <si>
+    <t>ecoinvent-3.10-cutoff-Base-2020</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON real, fossil ammonia</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON real, green ammonia</t>
+  </si>
+  <si>
+    <t>Dinitrogen monoxide</t>
+  </si>
+  <si>
+    <t>cooling energy, at -160 °C</t>
+  </si>
+  <si>
+    <t>cooling energy production, at -160 °C, propylene-ethylene-methane compression refrigeration system 1 MW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLO </t>
+  </si>
+  <si>
+    <t>hydrogen peroxide production, AO real, fossil hydrogen</t>
+  </si>
+  <si>
+    <t>hydrogen peroxide production, AO real, green hydrogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anthraquinone </t>
+  </si>
+  <si>
+    <t>market for anthraquinone</t>
+  </si>
+  <si>
+    <t>hydrogen, gaseous, medium pressure, merchant</t>
+  </si>
+  <si>
+    <t>market for hydrogen, gaseous, medium pressure, merchant</t>
+  </si>
+  <si>
+    <t>Carbon dioxide, fossil</t>
   </si>
 </sst>
 </file>
@@ -469,7 +491,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -523,6 +545,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -857,7 +882,7 @@
         <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="5"/>
@@ -881,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="3"/>
@@ -937,7 +962,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="3"/>
@@ -1000,10 +1025,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C11" s="11">
         <v>1</v>
@@ -1015,7 +1040,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
@@ -1038,7 +1063,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -1061,7 +1086,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1084,7 +1109,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -1107,7 +1132,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -1262,7 +1287,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H25" t="s">
         <v>14</v>
@@ -1285,7 +1310,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -1308,7 +1333,7 @@
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -1331,7 +1356,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -1354,7 +1379,7 @@
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -1377,7 +1402,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -1400,7 +1425,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -1423,7 +1448,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -1446,7 +1471,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -1469,7 +1494,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -1492,7 +1517,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -1515,7 +1540,7 @@
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -1538,7 +1563,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -1561,7 +1586,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -1584,7 +1609,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -1607,7 +1632,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -1630,7 +1655,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -1650,7 +1675,7 @@
         <v>72</v>
       </c>
       <c r="G42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H42" t="s">
         <v>19</v>
@@ -1670,7 +1695,7 @@
         <v>72</v>
       </c>
       <c r="G43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H43" t="s">
         <v>19</v>
@@ -1825,7 +1850,7 @@
         <v>3</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H53" t="s">
         <v>14</v>
@@ -1848,7 +1873,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -1871,7 +1896,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -1894,7 +1919,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -1905,7 +1930,7 @@
         <v>46</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C57" s="12">
         <v>5.28E-2</v>
@@ -1917,7 +1942,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -1940,7 +1965,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -1963,7 +1988,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -1986,7 +2011,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -2009,7 +2034,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -2032,7 +2057,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -2064,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="3"/>
@@ -2120,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="3"/>
@@ -2183,10 +2208,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9" s="11">
         <v>1</v>
@@ -2198,7 +2223,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -2221,7 +2246,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -2244,7 +2269,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -2268,7 +2293,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -2276,10 +2301,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" s="11">
         <v>0.17599999999999999</v>
@@ -2291,7 +2316,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -2314,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -2337,7 +2362,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -2360,7 +2385,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -2380,7 +2405,7 @@
         <v>22</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -2400,7 +2425,7 @@
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -2420,7 +2445,7 @@
         <v>22</v>
       </c>
       <c r="G19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H19" t="s">
         <v>19</v>
@@ -2441,7 +2466,7 @@
         <v>22</v>
       </c>
       <c r="G20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H20" t="s">
         <v>19</v>
@@ -2462,7 +2487,7 @@
         <v>87</v>
       </c>
       <c r="G21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H21" t="s">
         <v>19</v>
@@ -2617,7 +2642,7 @@
         <v>3</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>14</v>
@@ -2641,7 +2666,7 @@
         <v>3</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -2664,7 +2689,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -2685,7 +2710,7 @@
         <v>87</v>
       </c>
       <c r="G34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H34" t="s">
         <v>19</v>
@@ -2841,7 +2866,7 @@
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H44" t="s">
         <v>14</v>
@@ -2864,7 +2889,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -2887,7 +2912,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -2910,7 +2935,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -2933,7 +2958,7 @@
         <v>3</v>
       </c>
       <c r="G48" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -3089,7 +3114,7 @@
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H58" t="s">
         <v>14</v>
@@ -3113,7 +3138,7 @@
         <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -3134,7 +3159,7 @@
         <v>22</v>
       </c>
       <c r="G60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H60" t="s">
         <v>19</v>
@@ -3155,7 +3180,7 @@
         <v>87</v>
       </c>
       <c r="G61" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H61" t="s">
         <v>19</v>
@@ -3176,7 +3201,7 @@
         <v>28</v>
       </c>
       <c r="G62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H62" t="s">
         <v>19</v>
@@ -3190,12 +3215,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A007D5B7-6BDB-4C5E-BE6E-870683E782C1}">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3208,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="3"/>
@@ -3262,7 +3287,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="3"/>
@@ -3325,10 +3350,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C9" s="11">
         <v>1</v>
@@ -3340,7 +3365,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -3348,13 +3373,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C10" s="11">
-        <v>0.89440334956518253</v>
+        <v>0.81841178436562323</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -3363,7 +3388,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -3377,7 +3402,7 @@
         <v>88</v>
       </c>
       <c r="C11" s="12">
-        <v>-1.46247167513659E-3</v>
+        <v>-1.3561295696621E-3</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -3386,7 +3411,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -3400,7 +3425,7 @@
         <v>34</v>
       </c>
       <c r="C12" s="12">
-        <v>0.5473301234083312</v>
+        <v>5.0274869072994263E-2</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -3409,7 +3434,7 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -3423,7 +3448,7 @@
         <v>99</v>
       </c>
       <c r="C13" s="11">
-        <v>12.942566664203866</v>
+        <v>4.5210811135469591</v>
       </c>
       <c r="D13" t="s">
         <v>29</v>
@@ -3432,70 +3457,1230 @@
         <v>3</v>
       </c>
       <c r="G13" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9">
+        <v>1</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="11">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0.81841178436562323</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="12">
+        <v>-1.3561295696621E-3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="12">
+        <v>5.0274869072994263E-2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="11">
+        <v>4.5210811135469591</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="9">
+        <v>1</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="11">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s">
+        <v>3</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" t="s">
         <v>107</v>
       </c>
+      <c r="C38" s="11">
+        <v>0.96854616228089385</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s">
+        <v>111</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="12">
+        <v>-1.5899795617732801E-3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s">
+        <v>111</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="12">
+        <v>6.5803725096832189E-2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" t="s">
+        <v>3</v>
+      </c>
+      <c r="G40" t="s">
+        <v>111</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="11">
+        <v>19.451798344592323</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="11">
+        <v>0.57280190681669141</v>
+      </c>
+      <c r="D42" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" t="s">
+        <v>117</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="12">
+        <v>8.5167437462212083E-3</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" t="s">
+        <v>102</v>
+      </c>
+      <c r="H43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="23">
+        <v>1.5175217048085957E-5</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" t="s">
+        <v>102</v>
+      </c>
+      <c r="H44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="12">
+        <v>6.7533182458830068E-2</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" t="s">
+        <v>102</v>
+      </c>
+      <c r="H45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="16"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="16"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="9">
+        <v>1</v>
+      </c>
+      <c r="C50" s="16"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="16"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>113</v>
+      </c>
+      <c r="B55" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="11">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s">
+        <v>3</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H55" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="11">
+        <v>0.96854616228089385</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" t="s">
+        <v>3</v>
+      </c>
+      <c r="G56" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" s="12">
+        <v>-1.5899795617732801E-3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s">
+        <v>111</v>
+      </c>
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58" s="12">
+        <v>6.5803725096832189E-2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" t="s">
+        <v>111</v>
+      </c>
+      <c r="H58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="11">
+        <v>19.451798344592323</v>
+      </c>
+      <c r="D59" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H59" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" s="11">
+        <v>0.57280190681669141</v>
+      </c>
+      <c r="D60" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" t="s">
+        <v>117</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H60" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="12">
+        <v>8.5167437462212083E-3</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" t="s">
+        <v>102</v>
+      </c>
+      <c r="H61" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>114</v>
+      </c>
+      <c r="C62" s="23">
+        <v>1.5175217048085957E-5</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62" t="s">
+        <v>102</v>
+      </c>
+      <c r="H62" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="12">
+        <v>6.7533182458830068E-2</v>
+      </c>
+      <c r="D63" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" t="s">
+        <v>102</v>
+      </c>
+      <c r="H63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C34B5634-5AF1-473B-AC78-6B82FA75D54C}">
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="99.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="9">
+        <v>1</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="12">
+        <v>6.5856585494280195E-2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="12">
+        <v>3.0874916157909655E-3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>111</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="12">
+        <v>-5.7016971421526401E-4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="12">
+        <v>8.8525186072921841E-2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" t="s">
+        <v>111</v>
+      </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="11">
+        <v>2.8004251669216531</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="11">
-        <v>0.28078564277733647</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C15" s="11">
+        <v>1.9247124104337052</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="12">
-        <v>5.581483362661392</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>22</v>
-      </c>
       <c r="G15" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H15" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="12">
-        <v>3.3522421677960638E-5</v>
-      </c>
-      <c r="D16" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="11">
+        <v>6.5561271222166857E-3</v>
+      </c>
+      <c r="D16" t="s">
         <v>7</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H16" t="s">
         <v>19</v>
@@ -3503,19 +4688,20 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="12">
-        <v>6.8140848616508015E-2</v>
-      </c>
-      <c r="D17" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="11">
+        <f>2.9831*C11</f>
+        <v>9.2102962390660289E-3</v>
+      </c>
+      <c r="D17" t="s">
         <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H17" t="s">
         <v>19</v>
@@ -3523,19 +4709,20 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C18" s="12">
-        <v>1.4834478388868215E-3</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>7</v>
+        <f>0.4576*C11</f>
+        <v>1.4128361633859458E-3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H18" t="s">
         <v>19</v>
@@ -3556,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="3"/>
@@ -3610,7 +4797,7 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="3"/>
@@ -3673,10 +4860,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C28" s="11">
         <v>1</v>
@@ -3688,7 +4875,7 @@
         <v>3</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H28" t="s">
         <v>14</v>
@@ -3696,13 +4883,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C29" s="11">
-        <v>0.89440334956518253</v>
+        <v>6.5856585494280209E-2</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -3711,7 +4898,7 @@
         <v>3</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -3719,22 +4906,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="C30" s="12">
-        <v>-1.46247167513659E-3</v>
+        <v>3.0874916157909655E-3</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -3742,22 +4929,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="C31" s="12">
-        <v>0.5473301234083312</v>
+        <v>-5.7016971421526401E-4</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -3765,85 +4952,88 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="12">
+        <v>8.8525186072921841E-2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>99</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="11">
-        <v>12.942566664203866</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C33" s="11">
+        <v>2.8004251669216531</v>
+      </c>
+      <c r="D33" t="s">
         <v>29</v>
       </c>
-      <c r="E32" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="E33" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="11">
-        <v>0.28078564277733647</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="C34" s="11">
+        <v>1.9247124104337052</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G33" t="s">
-        <v>106</v>
-      </c>
-      <c r="H33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" s="12">
-        <v>5.581483362661392</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>22</v>
-      </c>
       <c r="G34" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H34" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" s="12">
-        <v>3.3522421677960638E-5</v>
-      </c>
-      <c r="D35" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="11">
+        <v>6.5561271222166857E-3</v>
+      </c>
+      <c r="D35" t="s">
         <v>7</v>
       </c>
       <c r="F35" t="s">
         <v>22</v>
       </c>
       <c r="G35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H35" t="s">
         <v>19</v>
@@ -3851,19 +5041,20 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="12">
-        <v>6.8140848616508015E-2</v>
-      </c>
-      <c r="D36" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="11">
+        <f>2.9831*C30</f>
+        <v>9.2102962390660289E-3</v>
+      </c>
+      <c r="D36" t="s">
         <v>7</v>
       </c>
       <c r="F36" t="s">
         <v>22</v>
       </c>
       <c r="G36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H36" t="s">
         <v>19</v>
@@ -3871,1257 +5062,27 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C37" s="12">
-        <v>1.4834478388868215E-3</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>7</v>
+        <f>0.4576*C30</f>
+        <v>1.4128361633859458E-3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
       </c>
       <c r="F37" t="s">
         <v>22</v>
       </c>
       <c r="G37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H37" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="16"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B41" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="9">
-        <v>1</v>
-      </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" t="s">
-        <v>114</v>
-      </c>
-      <c r="C47" s="11">
-        <v>1</v>
-      </c>
-      <c r="D47" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H47" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>110</v>
-      </c>
-      <c r="B48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" s="11">
-        <v>0.96853701735421172</v>
-      </c>
-      <c r="D48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G48" t="s">
-        <v>106</v>
-      </c>
-      <c r="H48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="12">
-        <v>-1.5899649003571401E-3</v>
-      </c>
-      <c r="D49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" t="s">
-        <v>106</v>
-      </c>
-      <c r="H49" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="12">
-        <v>6.5802604488272728E-2</v>
-      </c>
-      <c r="D50" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" t="s">
-        <v>3</v>
-      </c>
-      <c r="G50" t="s">
-        <v>106</v>
-      </c>
-      <c r="H50" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>99</v>
-      </c>
-      <c r="B51" t="s">
-        <v>99</v>
-      </c>
-      <c r="C51" s="11">
-        <v>5.302014103594094</v>
-      </c>
-      <c r="D51" t="s">
-        <v>29</v>
-      </c>
-      <c r="E51" t="s">
-        <v>3</v>
-      </c>
-      <c r="G51" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H51" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" s="11">
-        <v>0</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" t="s">
-        <v>106</v>
-      </c>
-      <c r="H52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>101</v>
-      </c>
-      <c r="C53" s="12">
-        <v>0.12230714647711328</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53" t="s">
-        <v>103</v>
-      </c>
-      <c r="H53" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="12">
-        <v>8.5186885398691459E-3</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" t="s">
-        <v>103</v>
-      </c>
-      <c r="H54" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" s="16"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B58" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="9">
-        <v>1</v>
-      </c>
-      <c r="C59" s="16"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B60" t="s">
-        <v>115</v>
-      </c>
-      <c r="C60" s="16"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="16"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>115</v>
-      </c>
-      <c r="B64" t="s">
-        <v>115</v>
-      </c>
-      <c r="C64" s="11">
-        <v>1</v>
-      </c>
-      <c r="D64" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" t="s">
-        <v>3</v>
-      </c>
-      <c r="G64" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H64" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>108</v>
-      </c>
-      <c r="B65" t="s">
-        <v>108</v>
-      </c>
-      <c r="C65" s="11">
-        <v>0.96853701735421172</v>
-      </c>
-      <c r="D65" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" t="s">
-        <v>3</v>
-      </c>
-      <c r="G65" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H65" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>89</v>
-      </c>
-      <c r="B66" t="s">
-        <v>88</v>
-      </c>
-      <c r="C66" s="12">
-        <v>-1.5899649003571401E-3</v>
-      </c>
-      <c r="D66" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" t="s">
-        <v>106</v>
-      </c>
-      <c r="H66" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>33</v>
-      </c>
-      <c r="B67" t="s">
-        <v>34</v>
-      </c>
-      <c r="C67" s="12">
-        <v>6.5802604488272728E-2</v>
-      </c>
-      <c r="D67" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" t="s">
-        <v>3</v>
-      </c>
-      <c r="G67" t="s">
-        <v>106</v>
-      </c>
-      <c r="H67" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>99</v>
-      </c>
-      <c r="B68" t="s">
-        <v>99</v>
-      </c>
-      <c r="C68" s="11">
-        <v>5.302014103594094</v>
-      </c>
-      <c r="D68" t="s">
-        <v>29</v>
-      </c>
-      <c r="E68" t="s">
-        <v>3</v>
-      </c>
-      <c r="G68" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H68" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B69" t="s">
-        <v>36</v>
-      </c>
-      <c r="C69" s="11">
-        <v>0</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" t="s">
-        <v>106</v>
-      </c>
-      <c r="H69" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
-        <v>101</v>
-      </c>
-      <c r="C70" s="12">
-        <v>0.12230714647711328</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
-        <v>22</v>
-      </c>
-      <c r="G70" t="s">
-        <v>103</v>
-      </c>
-      <c r="H70" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>21</v>
-      </c>
-      <c r="C71" s="12">
-        <v>8.5186885398691459E-3</v>
-      </c>
-      <c r="D71" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>22</v>
-      </c>
-      <c r="G71" t="s">
-        <v>103</v>
-      </c>
-      <c r="H71" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C73" s="16"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B75" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" s="16"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B76" s="9">
-        <v>1</v>
-      </c>
-      <c r="C76" s="16"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B77" t="s">
-        <v>116</v>
-      </c>
-      <c r="C77" s="16"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B78" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B79" s="3"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>116</v>
-      </c>
-      <c r="B81" t="s">
-        <v>116</v>
-      </c>
-      <c r="C81" s="11">
-        <v>1</v>
-      </c>
-      <c r="D81" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H81" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>110</v>
-      </c>
-      <c r="B82" t="s">
-        <v>109</v>
-      </c>
-      <c r="C82" s="11">
-        <v>0.81841178436562534</v>
-      </c>
-      <c r="D82" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" t="s">
-        <v>15</v>
-      </c>
-      <c r="G82" t="s">
-        <v>106</v>
-      </c>
-      <c r="H82" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>89</v>
-      </c>
-      <c r="B83" t="s">
-        <v>88</v>
-      </c>
-      <c r="C83" s="12">
-        <v>-1.3561295696621E-3</v>
-      </c>
-      <c r="D83" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" t="s">
-        <v>15</v>
-      </c>
-      <c r="G83" t="s">
-        <v>106</v>
-      </c>
-      <c r="H83" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>33</v>
-      </c>
-      <c r="B84" t="s">
-        <v>34</v>
-      </c>
-      <c r="C84" s="12">
-        <v>5.0274869081363735E-2</v>
-      </c>
-      <c r="D84" t="s">
-        <v>35</v>
-      </c>
-      <c r="E84" t="s">
-        <v>3</v>
-      </c>
-      <c r="G84" t="s">
-        <v>106</v>
-      </c>
-      <c r="H84" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>99</v>
-      </c>
-      <c r="B85" t="s">
-        <v>99</v>
-      </c>
-      <c r="C85" s="11">
-        <v>4.5210811141584566</v>
-      </c>
-      <c r="D85" t="s">
-        <v>29</v>
-      </c>
-      <c r="E85" t="s">
-        <v>3</v>
-      </c>
-      <c r="G85" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H85" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B86" t="s">
-        <v>36</v>
-      </c>
-      <c r="C86" s="11">
-        <v>0</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G86" t="s">
-        <v>106</v>
-      </c>
-      <c r="H86" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
-        <v>101</v>
-      </c>
-      <c r="C87" s="12">
-        <v>0</v>
-      </c>
-      <c r="D87" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>22</v>
-      </c>
-      <c r="G87" t="s">
-        <v>103</v>
-      </c>
-      <c r="H87" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>21</v>
-      </c>
-      <c r="C88" s="12">
-        <v>0</v>
-      </c>
-      <c r="D88" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" t="s">
-        <v>22</v>
-      </c>
-      <c r="G88" t="s">
-        <v>103</v>
-      </c>
-      <c r="H88" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C90" s="16"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B91" s="6"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B92" t="s">
-        <v>3</v>
-      </c>
-      <c r="C92" s="16"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B93" s="9">
-        <v>1</v>
-      </c>
-      <c r="C93" s="16"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B94" t="s">
-        <v>117</v>
-      </c>
-      <c r="C94" s="16"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B95" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="16"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B96" s="3"/>
-      <c r="C96" s="16"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>117</v>
-      </c>
-      <c r="B98" t="s">
-        <v>117</v>
-      </c>
-      <c r="C98" s="11">
-        <v>1</v>
-      </c>
-      <c r="D98" t="s">
-        <v>7</v>
-      </c>
-      <c r="E98" t="s">
-        <v>3</v>
-      </c>
-      <c r="G98" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H98" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>108</v>
-      </c>
-      <c r="B99" t="s">
-        <v>108</v>
-      </c>
-      <c r="C99" s="11">
-        <v>0.81841178436562534</v>
-      </c>
-      <c r="D99" t="s">
-        <v>7</v>
-      </c>
-      <c r="E99" t="s">
-        <v>3</v>
-      </c>
-      <c r="G99" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H99" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>89</v>
-      </c>
-      <c r="B100" t="s">
-        <v>88</v>
-      </c>
-      <c r="C100" s="12">
-        <v>-1.3561295696621E-3</v>
-      </c>
-      <c r="D100" t="s">
-        <v>17</v>
-      </c>
-      <c r="E100" t="s">
-        <v>15</v>
-      </c>
-      <c r="G100" t="s">
-        <v>106</v>
-      </c>
-      <c r="H100" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>33</v>
-      </c>
-      <c r="B101" t="s">
-        <v>34</v>
-      </c>
-      <c r="C101" s="12">
-        <v>5.0274869081363735E-2</v>
-      </c>
-      <c r="D101" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" t="s">
-        <v>106</v>
-      </c>
-      <c r="H101" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>99</v>
-      </c>
-      <c r="B102" t="s">
-        <v>99</v>
-      </c>
-      <c r="C102" s="11">
-        <v>4.5210811141584566</v>
-      </c>
-      <c r="D102" t="s">
-        <v>29</v>
-      </c>
-      <c r="E102" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H102" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B103" t="s">
-        <v>36</v>
-      </c>
-      <c r="C103" s="11">
-        <v>0</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G103" t="s">
-        <v>106</v>
-      </c>
-      <c r="H103" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
-        <v>101</v>
-      </c>
-      <c r="C104" s="12">
-        <v>0</v>
-      </c>
-      <c r="D104" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F104" t="s">
-        <v>22</v>
-      </c>
-      <c r="G104" t="s">
-        <v>103</v>
-      </c>
-      <c r="H104" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B105" t="s">
-        <v>21</v>
-      </c>
-      <c r="C105" s="12">
-        <v>0</v>
-      </c>
-      <c r="D105" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F105" t="s">
-        <v>22</v>
-      </c>
-      <c r="G105" t="s">
-        <v>103</v>
-      </c>
-      <c r="H105" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/inventories_ei310.xlsx
+++ b/data/inventories_ei310.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11179947-0382-4CF6-9706-C59C2E9AA66F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0FEF68-E419-4A1F-94DF-4746AAC7B520}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="3" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogen" sheetId="14" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="127">
   <si>
     <t>Activity</t>
   </si>
@@ -403,6 +403,12 @@
   </si>
   <si>
     <t>Carbon dioxide, fossil</t>
+  </si>
+  <si>
+    <t>market for benzene</t>
+  </si>
+  <si>
+    <t>benzene</t>
   </si>
 </sst>
 </file>
@@ -4372,7 +4378,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C34B5634-5AF1-473B-AC78-6B82FA75D54C}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.85546875" bestFit="1" customWidth="1"/>
@@ -4576,18 +4582,18 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="C12" s="12">
-        <v>-5.7016971421526401E-4</v>
+        <v>1.9300000000000001E-3</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
@@ -4599,19 +4605,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="C13" s="12">
-        <v>8.8525186072921841E-2</v>
+        <v>-5.7016971421526401E-4</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
         <v>111</v>
@@ -4622,141 +4628,152 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="12">
+        <v>8.8525186072921841E-2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>99</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C15" s="11">
         <v>2.8004251669216531</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>29</v>
       </c>
-      <c r="E14" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="21" t="s">
+      <c r="E15" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="H14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C16" s="11">
         <v>1.9247124104337052</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G15" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="11">
-        <v>6.5561271222166857E-3</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
       <c r="G16" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="11">
+        <v>6.5561271222166857E-3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C18" s="11">
         <f>2.9831*C11</f>
         <v>9.2102962390660289E-3</v>
       </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
         <v>22</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G18" t="s">
         <v>102</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C19" s="12">
         <f>0.4576*C11</f>
         <v>1.4128361633859458E-3</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>17</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F19" t="s">
         <v>22</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G19" t="s">
         <v>102</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B21" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="6"/>
       <c r="C21" s="16"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -4766,11 +4783,9 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B22" s="6"/>
       <c r="C22" s="16"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -4780,10 +4795,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="9">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="3"/>
@@ -4794,10 +4809,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>119</v>
+        <v>4</v>
+      </c>
+      <c r="B24" s="9">
+        <v>1</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="3"/>
@@ -4808,10 +4823,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="3"/>
@@ -4821,10 +4836,12 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
       <c r="C26" s="16"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -4833,63 +4850,52 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C28" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D28" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E28" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H28" s="7" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" s="11">
-        <v>1</v>
-      </c>
-      <c r="D28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" t="s">
-        <v>3</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="H28" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C29" s="11">
-        <v>6.5856585494280209E-2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4901,18 +4907,18 @@
         <v>105</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="12">
-        <v>3.0874916157909655E-3</v>
+        <v>104</v>
+      </c>
+      <c r="C30" s="11">
+        <v>6.5856585494280209E-2</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4920,8 +4926,8 @@
       <c r="E30" t="s">
         <v>3</v>
       </c>
-      <c r="G30" t="s">
-        <v>111</v>
+      <c r="G30" s="21" t="s">
+        <v>105</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -4929,19 +4935,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="C31" s="12">
-        <v>-5.7016971421526401E-4</v>
+        <v>3.0874916157909655E-3</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G31" t="s">
         <v>111</v>
@@ -4952,19 +4958,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="C32" s="12">
-        <v>8.8525186072921841E-2</v>
+        <v>1.9300000000000001E-3</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" t="s">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="G32" t="s">
         <v>111</v>
@@ -4975,101 +4981,105 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="12">
+        <v>-5.7016971421526401E-4</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s">
+        <v>111</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="12">
+        <v>8.8525186072921841E-2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" t="s">
+        <v>3</v>
+      </c>
+      <c r="G34" t="s">
+        <v>111</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>99</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B35" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C35" s="11">
         <v>2.8004251669216531</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D35" t="s">
         <v>29</v>
       </c>
-      <c r="E33" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="21" t="s">
+      <c r="E35" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="H33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C36" s="11">
         <v>1.9247124104337052</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G34" t="s">
-        <v>111</v>
-      </c>
-      <c r="H34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35" s="11">
-        <v>6.5561271222166857E-3</v>
-      </c>
-      <c r="D35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>22</v>
-      </c>
-      <c r="G35" t="s">
-        <v>102</v>
-      </c>
-      <c r="H35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="11">
-        <f>2.9831*C30</f>
-        <v>9.2102962390660289E-3</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>22</v>
-      </c>
       <c r="G36" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H36" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="12">
-        <f>0.4576*C30</f>
-        <v>1.4128361633859458E-3</v>
+        <v>90</v>
+      </c>
+      <c r="C37" s="11">
+        <v>6.5561271222166857E-3</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
         <v>22</v>
@@ -5078,6 +5088,48 @@
         <v>102</v>
       </c>
       <c r="H37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="11">
+        <f>2.9831*C31</f>
+        <v>9.2102962390660289E-3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="12">
+        <f>0.4576*C31</f>
+        <v>1.4128361633859458E-3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" t="s">
+        <v>102</v>
+      </c>
+      <c r="H39" t="s">
         <v>19</v>
       </c>
     </row>

--- a/data/inventories_ei310.xlsx
+++ b/data/inventories_ei310.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0FEF68-E419-4A1F-94DF-4746AAC7B520}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40399F58-DCCB-4FE8-A2F6-77C835E753C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="3" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
@@ -357,21 +357,9 @@
     <t>ammonia, anhydrous, liquid</t>
   </si>
   <si>
-    <t>nitrous oxide production, AON ideal, fossil ammonia</t>
-  </si>
-  <si>
-    <t>nitrous oxide production, AON ideal, green ammonia</t>
-  </si>
-  <si>
     <t>ecoinvent-3.10-cutoff-Base-2020</t>
   </si>
   <si>
-    <t>nitrous oxide production, AON real, fossil ammonia</t>
-  </si>
-  <si>
-    <t>nitrous oxide production, AON real, green ammonia</t>
-  </si>
-  <si>
     <t>Dinitrogen monoxide</t>
   </si>
   <si>
@@ -384,12 +372,6 @@
     <t xml:space="preserve">GLO </t>
   </si>
   <si>
-    <t>hydrogen peroxide production, AO real, fossil hydrogen</t>
-  </si>
-  <si>
-    <t>hydrogen peroxide production, AO real, green hydrogen</t>
-  </si>
-  <si>
     <t xml:space="preserve">anthraquinone </t>
   </si>
   <si>
@@ -409,6 +391,24 @@
   </si>
   <si>
     <t>benzene</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON 88, fossil ammonia</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON 100, fossil ammonia</t>
+  </si>
+  <si>
+    <t>hydrogen peroxide production, AO, green hydrogen</t>
+  </si>
+  <si>
+    <t>hydrogen peroxide production, AO, fossil hydrogen</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON 100, green ammonia</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON 88, green ammonia</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1092,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1115,7 +1115,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -1138,7 +1138,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -1362,7 +1362,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -1385,7 +1385,7 @@
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -1408,7 +1408,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -1431,7 +1431,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -1454,7 +1454,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -1477,7 +1477,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -1500,7 +1500,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -1523,7 +1523,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -1546,7 +1546,7 @@
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -1569,7 +1569,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -1592,7 +1592,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -1615,7 +1615,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -1638,7 +1638,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -1661,7 +1661,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -1879,7 +1879,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -1902,7 +1902,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -1948,7 +1948,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -1971,7 +1971,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -1994,7 +1994,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -2017,7 +2017,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -2040,7 +2040,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -2063,7 +2063,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -2345,7 +2345,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -2368,7 +2368,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -2391,7 +2391,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -2695,7 +2695,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -2895,7 +2895,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -2918,7 +2918,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -2941,7 +2941,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -2964,7 +2964,7 @@
         <v>3</v>
       </c>
       <c r="G48" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -3144,7 +3144,7 @@
         <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="3"/>
@@ -3293,7 +3293,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="3"/>
@@ -3356,10 +3356,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C9" s="11">
         <v>1</v>
@@ -3394,7 +3394,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -3417,7 +3417,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -3440,7 +3440,7 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="3"/>
@@ -3538,7 +3538,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="3"/>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C23" s="11">
         <v>1</v>
@@ -3662,7 +3662,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -3685,7 +3685,7 @@
         <v>3</v>
       </c>
       <c r="G26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="3"/>
@@ -3783,7 +3783,7 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C33" s="16"/>
       <c r="D33" s="3"/>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C37" s="11">
         <v>1</v>
@@ -3875,7 +3875,7 @@
         <v>107</v>
       </c>
       <c r="C38" s="11">
-        <v>0.96854616228089385</v>
+        <v>0.91964998512365381</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -3884,7 +3884,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -3898,7 +3898,7 @@
         <v>88</v>
       </c>
       <c r="C39" s="12">
-        <v>-1.5899795617732801E-3</v>
+        <v>-1.51353683099332E-3</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -3907,7 +3907,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -3921,7 +3921,7 @@
         <v>34</v>
       </c>
       <c r="C40" s="12">
-        <v>6.5803725096832189E-2</v>
+        <v>6.0754013722332099E-2</v>
       </c>
       <c r="D40" t="s">
         <v>35</v>
@@ -3930,7 +3930,7 @@
         <v>3</v>
       </c>
       <c r="G40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -3944,7 +3944,7 @@
         <v>99</v>
       </c>
       <c r="C41" s="11">
-        <v>19.451798344592323</v>
+        <v>4.6646502651840436</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
@@ -3961,22 +3961,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C42" s="11">
-        <v>0.57280190681669141</v>
+        <v>0.50722214107282404</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G42" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -3987,7 +3987,7 @@
         <v>101</v>
       </c>
       <c r="C43" s="12">
-        <v>8.5167437462212083E-3</v>
+        <v>7.842128857001375E-2</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>7</v>
@@ -4004,10 +4004,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="23">
-        <v>1.5175217048085957E-5</v>
+        <v>110</v>
+      </c>
+      <c r="C44" s="13">
+        <v>2.0022743606470884E-4</v>
       </c>
       <c r="D44" s="22" t="s">
         <v>7</v>
@@ -4027,7 +4027,7 @@
         <v>21</v>
       </c>
       <c r="C45" s="12">
-        <v>6.7533182458830068E-2</v>
+        <v>1.4556189599066783E-2</v>
       </c>
       <c r="D45" s="22" t="s">
         <v>7</v>
@@ -4057,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="3"/>
@@ -4111,7 +4111,7 @@
         <v>5</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C51" s="16"/>
       <c r="D51" s="3"/>
@@ -4174,10 +4174,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B55" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C55" s="11">
         <v>1</v>
@@ -4203,7 +4203,7 @@
         <v>106</v>
       </c>
       <c r="C56" s="11">
-        <v>0.96854616228089385</v>
+        <v>0.91964998512365381</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -4226,7 +4226,7 @@
         <v>88</v>
       </c>
       <c r="C57" s="12">
-        <v>-1.5899795617732801E-3</v>
+        <v>-1.51353683099332E-3</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -4235,7 +4235,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -4249,7 +4249,7 @@
         <v>34</v>
       </c>
       <c r="C58" s="12">
-        <v>6.5803725096832189E-2</v>
+        <v>6.0754013722332099E-2</v>
       </c>
       <c r="D58" t="s">
         <v>35</v>
@@ -4258,7 +4258,7 @@
         <v>3</v>
       </c>
       <c r="G58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -4272,7 +4272,7 @@
         <v>99</v>
       </c>
       <c r="C59" s="11">
-        <v>19.451798344592323</v>
+        <v>4.6646502651840436</v>
       </c>
       <c r="D59" t="s">
         <v>29</v>
@@ -4289,22 +4289,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C60" s="11">
-        <v>0.57280190681669141</v>
+        <v>0.50722214107282404</v>
       </c>
       <c r="D60" t="s">
         <v>29</v>
       </c>
       <c r="E60" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G60" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -4315,7 +4315,7 @@
         <v>101</v>
       </c>
       <c r="C61" s="12">
-        <v>8.5167437462212083E-3</v>
+        <v>7.842128857001375E-2</v>
       </c>
       <c r="D61" s="22" t="s">
         <v>7</v>
@@ -4332,10 +4332,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C62" s="23">
-        <v>1.5175217048085957E-5</v>
+        <v>2.0022743606470884E-4</v>
       </c>
       <c r="D62" s="22" t="s">
         <v>7</v>
@@ -4355,7 +4355,7 @@
         <v>21</v>
       </c>
       <c r="C63" s="12">
-        <v>6.7533182458830068E-2</v>
+        <v>1.4556189599066783E-2</v>
       </c>
       <c r="D63" s="22" t="s">
         <v>7</v>
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="3"/>
@@ -4450,7 +4450,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="3"/>
@@ -4513,10 +4513,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C9" s="11">
         <v>1</v>
@@ -4536,10 +4536,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C10" s="12">
         <v>6.5856585494280195E-2</v>
@@ -4551,7 +4551,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -4559,10 +4559,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C11" s="12">
         <v>3.0874916157909655E-3</v>
@@ -4574,7 +4574,7 @@
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C12" s="12">
         <v>1.9300000000000001E-3</v>
@@ -4597,7 +4597,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -4620,7 +4620,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -4643,7 +4643,7 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -4689,7 +4689,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -4717,7 +4717,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C18" s="11">
         <f>2.9831*C11</f>
@@ -4772,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="3"/>
@@ -4826,7 +4826,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="3"/>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C29" s="11">
         <v>1</v>
@@ -4935,10 +4935,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C31" s="12">
         <v>3.0874916157909655E-3</v>
@@ -4950,7 +4950,7 @@
         <v>3</v>
       </c>
       <c r="G31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -4958,10 +4958,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C32" s="12">
         <v>1.9300000000000001E-3</v>
@@ -4973,7 +4973,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -4996,7 +4996,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -5019,7 +5019,7 @@
         <v>3</v>
       </c>
       <c r="G34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -5065,7 +5065,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -5093,7 +5093,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C38" s="11">
         <f>2.9831*C31</f>

--- a/data/inventories_ei310.xlsx
+++ b/data/inventories_ei310.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40399F58-DCCB-4FE8-A2F6-77C835E753C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D339D8-EDE4-4387-96C1-02499A406FE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="3" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogen" sheetId="14" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="131">
   <si>
     <t>Activity</t>
   </si>
@@ -409,6 +409,18 @@
   </si>
   <si>
     <t>nitrous oxide production, AON 88, green ammonia</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>market for gold</t>
+  </si>
+  <si>
+    <t>market for palladium</t>
+  </si>
+  <si>
+    <t>palladium</t>
   </si>
 </sst>
 </file>
@@ -3221,7 +3233,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A007D5B7-6BDB-4C5E-BE6E-870683E782C1}">
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.85546875" bestFit="1" customWidth="1"/>
@@ -3915,16 +3927,16 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="12">
-        <v>6.0754013722332099E-2</v>
+        <v>128</v>
+      </c>
+      <c r="C40" s="13">
+        <v>9.1406803346159078E-8</v>
       </c>
       <c r="D40" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
         <v>3</v>
@@ -3938,22 +3950,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" s="11">
-        <v>4.6646502651840436</v>
+        <v>34</v>
+      </c>
+      <c r="C41" s="12">
+        <v>6.0754013722332099E-2</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E41" t="s">
         <v>3</v>
       </c>
-      <c r="G41" s="21" t="s">
-        <v>105</v>
+      <c r="G41" t="s">
+        <v>109</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -3961,53 +3973,56 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C42" s="11">
-        <v>0.50722214107282404</v>
+        <v>4.6646502651840436</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
       </c>
       <c r="E42" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="11">
+        <v>0.50722214107282404</v>
+      </c>
+      <c r="D43" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" t="s">
         <v>113</v>
       </c>
-      <c r="G42" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="H42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>101</v>
-      </c>
-      <c r="C43" s="12">
-        <v>7.842128857001375E-2</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43" t="s">
-        <v>102</v>
+      <c r="G43" s="21" t="s">
+        <v>109</v>
       </c>
       <c r="H43" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="13">
-        <v>2.0022743606470884E-4</v>
+        <v>101</v>
+      </c>
+      <c r="C44" s="12">
+        <v>7.842128857001375E-2</v>
       </c>
       <c r="D44" s="22" t="s">
         <v>7</v>
@@ -4024,10 +4039,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="12">
-        <v>1.4556189599066783E-2</v>
+        <v>110</v>
+      </c>
+      <c r="C45" s="13">
+        <v>2.0022743606470884E-4</v>
       </c>
       <c r="D45" s="22" t="s">
         <v>7</v>
@@ -4043,34 +4058,42 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="12">
+        <v>1.4556189599066783E-2</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" t="s">
+        <v>102</v>
+      </c>
+      <c r="H46" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B48" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C47" s="16"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B48" s="6"/>
       <c r="C48" s="16"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4080,11 +4103,9 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B49" t="s">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B49" s="6"/>
       <c r="C49" s="16"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -4094,10 +4115,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="9">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
       </c>
       <c r="C50" s="16"/>
       <c r="D50" s="3"/>
@@ -4108,10 +4129,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" t="s">
-        <v>126</v>
+        <v>4</v>
+      </c>
+      <c r="B51" s="9">
+        <v>1</v>
       </c>
       <c r="C51" s="16"/>
       <c r="D51" s="3"/>
@@ -4122,10 +4143,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="C52" s="16"/>
       <c r="D52" s="3"/>
@@ -4135,10 +4156,12 @@
       <c r="H52" s="3"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B53" s="3"/>
+      <c r="A53" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
       <c r="C53" s="16"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -4147,63 +4170,52 @@
       <c r="H53" s="3"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B55" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C55" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D55" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E55" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F55" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G55" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H54" s="7" t="s">
+      <c r="H55" s="7" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>126</v>
-      </c>
-      <c r="B55" t="s">
-        <v>126</v>
-      </c>
-      <c r="C55" s="11">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" t="s">
-        <v>3</v>
-      </c>
-      <c r="G55" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="H55" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C56" s="11">
-        <v>0.91964998512365381</v>
+        <v>1</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -4215,27 +4227,27 @@
         <v>105</v>
       </c>
       <c r="H56" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
-      </c>
-      <c r="C57" s="12">
-        <v>-1.51353683099332E-3</v>
+        <v>106</v>
+      </c>
+      <c r="C57" s="11">
+        <v>0.91964998512365381</v>
       </c>
       <c r="D57" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E57" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" t="s">
-        <v>109</v>
+        <v>3</v>
+      </c>
+      <c r="G57" s="21" t="s">
+        <v>105</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -4243,19 +4255,19 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="C58" s="12">
-        <v>6.0754013722332099E-2</v>
+        <v>-1.51353683099332E-3</v>
       </c>
       <c r="D58" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E58" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
         <v>109</v>
@@ -4266,22 +4278,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
-      </c>
-      <c r="C59" s="11">
-        <v>4.6646502651840436</v>
+        <v>128</v>
+      </c>
+      <c r="C59" s="13">
+        <v>9.1406803346159078E-8</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E59" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="21" t="s">
-        <v>105</v>
+      <c r="G59" t="s">
+        <v>109</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -4289,73 +4301,79 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" s="12">
+        <v>6.0754013722332099E-2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>35</v>
+      </c>
+      <c r="E60" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" t="s">
+        <v>109</v>
+      </c>
+      <c r="H60" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="11">
+        <v>4.6646502651840436</v>
+      </c>
+      <c r="D61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" t="s">
+        <v>3</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H61" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>111</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B62" t="s">
         <v>112</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C62" s="11">
         <v>0.50722214107282404</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D62" t="s">
         <v>29</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E62" t="s">
         <v>113</v>
       </c>
-      <c r="G60" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="H60" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>101</v>
-      </c>
-      <c r="C61" s="12">
-        <v>7.842128857001375E-2</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" t="s">
-        <v>102</v>
-      </c>
-      <c r="H61" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" s="23">
-        <v>2.0022743606470884E-4</v>
-      </c>
-      <c r="D62" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>22</v>
-      </c>
-      <c r="G62" t="s">
-        <v>102</v>
+      <c r="G62" s="21" t="s">
+        <v>109</v>
       </c>
       <c r="H62" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="C63" s="12">
-        <v>1.4556189599066783E-2</v>
+        <v>7.842128857001375E-2</v>
       </c>
       <c r="D63" s="22" t="s">
         <v>7</v>
@@ -4367,6 +4385,46 @@
         <v>102</v>
       </c>
       <c r="H63" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" s="23">
+        <v>2.0022743606470884E-4</v>
+      </c>
+      <c r="D64" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" t="s">
+        <v>102</v>
+      </c>
+      <c r="H64" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="12">
+        <v>1.4556189599066783E-2</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F65" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" t="s">
+        <v>102</v>
+      </c>
+      <c r="H65" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4378,7 +4436,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C34B5634-5AF1-473B-AC78-6B82FA75D54C}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.85546875" bestFit="1" customWidth="1"/>
@@ -4628,16 +4686,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="12">
-        <v>8.8525186072921841E-2</v>
+        <v>129</v>
+      </c>
+      <c r="C14" s="13">
+        <v>2.5650000000000022E-9</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
         <v>3</v>
@@ -4651,141 +4709,152 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="12">
+        <v>8.8525186072921841E-2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>99</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C16" s="11">
         <v>2.8004251669216531</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>29</v>
       </c>
-      <c r="E15" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="21" t="s">
+      <c r="E16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="H15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C17" s="11">
         <v>1.9247124104337052</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G16" t="s">
-        <v>109</v>
-      </c>
-      <c r="H16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="11">
-        <v>6.5561271222166857E-3</v>
-      </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>22</v>
-      </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="11">
+        <v>6.5561271222166857E-3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C19" s="11">
         <f>2.9831*C11</f>
         <v>9.2102962390660289E-3</v>
       </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
         <v>22</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G19" t="s">
         <v>102</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C20" s="12">
         <f>0.4576*C11</f>
         <v>1.4128361633859458E-3</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>17</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F20" t="s">
         <v>22</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G20" t="s">
         <v>102</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-    </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B22" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="6"/>
       <c r="C22" s="16"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -4795,11 +4864,9 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B23" s="6"/>
       <c r="C23" s="16"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -4809,10 +4876,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="9">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="3"/>
@@ -4823,10 +4890,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>123</v>
+        <v>4</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="3"/>
@@ -4837,10 +4904,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="3"/>
@@ -4850,10 +4917,12 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="3"/>
+      <c r="A27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
       <c r="C27" s="16"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -4862,63 +4931,52 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C29" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H29" s="7" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>123</v>
-      </c>
-      <c r="B29" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="11">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="H29" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C30" s="11">
-        <v>6.5856585494280209E-2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4930,18 +4988,18 @@
         <v>105</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" s="12">
-        <v>3.0874916157909655E-3</v>
+        <v>104</v>
+      </c>
+      <c r="C31" s="11">
+        <v>6.5856585494280209E-2</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4949,8 +5007,8 @@
       <c r="E31" t="s">
         <v>3</v>
       </c>
-      <c r="G31" t="s">
-        <v>109</v>
+      <c r="G31" s="21" t="s">
+        <v>105</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -4958,19 +5016,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C32" s="12">
-        <v>1.9300000000000001E-3</v>
+        <v>3.0874916157909655E-3</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>15</v>
+      <c r="E32" t="s">
+        <v>3</v>
       </c>
       <c r="G32" t="s">
         <v>109</v>
@@ -4981,18 +5039,18 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="C33" s="12">
-        <v>-5.7016971421526401E-4</v>
+        <v>1.9300000000000001E-3</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G33" t="s">
@@ -5004,19 +5062,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="C34" s="12">
-        <v>8.8525186072921841E-2</v>
+        <v>-5.7016971421526401E-4</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E34" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G34" t="s">
         <v>109</v>
@@ -5027,101 +5085,105 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" s="13">
+        <v>2.5650000000000022E-9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" t="s">
+        <v>109</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="12">
+        <v>8.8525186072921841E-2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" t="s">
+        <v>3</v>
+      </c>
+      <c r="G36" t="s">
+        <v>109</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>99</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B37" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C37" s="11">
         <v>2.8004251669216531</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D37" t="s">
         <v>29</v>
       </c>
-      <c r="E35" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="21" t="s">
+      <c r="E37" t="s">
+        <v>3</v>
+      </c>
+      <c r="G37" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="H35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B38" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C38" s="11">
         <v>1.9247124104337052</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G36" t="s">
-        <v>109</v>
-      </c>
-      <c r="H36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="11">
-        <v>6.5561271222166857E-3</v>
-      </c>
-      <c r="D37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37" t="s">
-        <v>102</v>
-      </c>
-      <c r="H37" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>118</v>
-      </c>
-      <c r="C38" s="11">
-        <f>2.9831*C31</f>
-        <v>9.2102962390660289E-3</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>22</v>
-      </c>
       <c r="G38" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H38" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="12">
-        <f>0.4576*C31</f>
-        <v>1.4128361633859458E-3</v>
+        <v>90</v>
+      </c>
+      <c r="C39" s="11">
+        <v>6.5561271222166857E-3</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
         <v>22</v>
@@ -5130,6 +5192,48 @@
         <v>102</v>
       </c>
       <c r="H39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="11">
+        <f>2.9831*C32</f>
+        <v>9.2102962390660289E-3</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" t="s">
+        <v>102</v>
+      </c>
+      <c r="H40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="12">
+        <f>0.4576*C32</f>
+        <v>1.4128361633859458E-3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" t="s">
+        <v>102</v>
+      </c>
+      <c r="H41" t="s">
         <v>19</v>
       </c>
     </row>

--- a/data/inventories_ei310.xlsx
+++ b/data/inventories_ei310.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D339D8-EDE4-4387-96C1-02499A406FE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B4DC5D-D9D3-4837-BA64-23010486F629}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="136">
   <si>
     <t>Activity</t>
   </si>
@@ -393,9 +393,6 @@
     <t>benzene</t>
   </si>
   <si>
-    <t>nitrous oxide production, AON 88, fossil ammonia</t>
-  </si>
-  <si>
     <t>nitrous oxide production, AON 100, fossil ammonia</t>
   </si>
   <si>
@@ -408,9 +405,6 @@
     <t>nitrous oxide production, AON 100, green ammonia</t>
   </si>
   <si>
-    <t>nitrous oxide production, AON 88, green ammonia</t>
-  </si>
-  <si>
     <t>gold</t>
   </si>
   <si>
@@ -421,6 +415,27 @@
   </si>
   <si>
     <t>palladium</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON 90 membrane, fossil ammonia</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON 90 membrane, green ammonia</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON 90 cryogenic, fossil ammonia</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, AON 90 cryogenic, green ammonia</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, BAU, fossil ammonia</t>
+  </si>
+  <si>
+    <t>nitrous oxide production, BAU, green ammonia</t>
+  </si>
+  <si>
+    <t>Nitric acid</t>
   </si>
 </sst>
 </file>
@@ -509,7 +524,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -564,6 +579,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3233,10 +3251,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A007D5B7-6BDB-4C5E-BE6E-870683E782C1}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
@@ -3251,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="3"/>
@@ -3305,7 +3323,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="3"/>
@@ -3368,10 +3386,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C9" s="11">
         <v>1</v>
@@ -3397,7 +3415,7 @@
         <v>107</v>
       </c>
       <c r="C10" s="11">
-        <v>0.81841178436562323</v>
+        <v>0.81841179834052924</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -3420,7 +3438,7 @@
         <v>88</v>
       </c>
       <c r="C11" s="12">
-        <v>-1.3561295696621E-3</v>
+        <v>-1.3561296098945201E-3</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -3443,7 +3461,7 @@
         <v>34</v>
       </c>
       <c r="C12" s="12">
-        <v>5.0274869072994263E-2</v>
+        <v>5.0274871051467697E-2</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -3466,7 +3484,7 @@
         <v>99</v>
       </c>
       <c r="C13" s="11">
-        <v>4.5210811135469591</v>
+        <v>4.5210811907473172</v>
       </c>
       <c r="D13" t="s">
         <v>29</v>
@@ -3496,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="3"/>
@@ -3550,7 +3568,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="3"/>
@@ -3613,10 +3631,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C23" s="11">
         <v>1</v>
@@ -3642,7 +3660,7 @@
         <v>106</v>
       </c>
       <c r="C24" s="11">
-        <v>0.81841178436562323</v>
+        <v>0.81841179834052924</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -3664,8 +3682,8 @@
       <c r="B25" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="12">
-        <v>-1.3561295696621E-3</v>
+      <c r="C25" s="11">
+        <v>-1.3561296098945201E-3</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -3687,8 +3705,8 @@
       <c r="B26" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="12">
-        <v>5.0274869072994263E-2</v>
+      <c r="C26" s="11">
+        <v>5.0274871051467697E-2</v>
       </c>
       <c r="D26" t="s">
         <v>35</v>
@@ -3711,7 +3729,7 @@
         <v>99</v>
       </c>
       <c r="C27" s="11">
-        <v>4.5210811135469591</v>
+        <v>4.5210811907473172</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
@@ -3741,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="3"/>
@@ -3795,7 +3813,7 @@
         <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C33" s="16"/>
       <c r="D33" s="3"/>
@@ -3858,10 +3876,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C37" s="11">
         <v>1</v>
@@ -3887,7 +3905,7 @@
         <v>107</v>
       </c>
       <c r="C38" s="11">
-        <v>0.91964998512365381</v>
+        <v>0.90659390280881114</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -3910,7 +3928,7 @@
         <v>88</v>
       </c>
       <c r="C39" s="12">
-        <v>-1.51353683099332E-3</v>
+        <v>-1.4931786697317401E-3</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -3927,13 +3945,13 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" s="13">
-        <v>9.1406803346159078E-8</v>
+        <v>126</v>
+      </c>
+      <c r="C40" s="12">
+        <v>0</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -3956,7 +3974,7 @@
         <v>34</v>
       </c>
       <c r="C41" s="12">
-        <v>6.0754013722332099E-2</v>
+        <v>5.9409513565910815E-2</v>
       </c>
       <c r="D41" t="s">
         <v>35</v>
@@ -3979,7 +3997,7 @@
         <v>99</v>
       </c>
       <c r="C42" s="11">
-        <v>4.6646502651840436</v>
+        <v>4.5997084648075042</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
@@ -4002,7 +4020,7 @@
         <v>112</v>
       </c>
       <c r="C43" s="11">
-        <v>0.50722214107282404</v>
+        <v>0.59735221660353577</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -4022,7 +4040,7 @@
         <v>101</v>
       </c>
       <c r="C44" s="12">
-        <v>7.842128857001375E-2</v>
+        <v>7.4326007558944585E-2</v>
       </c>
       <c r="D44" s="22" t="s">
         <v>7</v>
@@ -4042,7 +4060,7 @@
         <v>110</v>
       </c>
       <c r="C45" s="13">
-        <v>2.0022743606470884E-4</v>
+        <v>1.0010620753264169E-4</v>
       </c>
       <c r="D45" s="22" t="s">
         <v>7</v>
@@ -4062,7 +4080,7 @@
         <v>21</v>
       </c>
       <c r="C46" s="12">
-        <v>1.4556189599066783E-2</v>
+        <v>0</v>
       </c>
       <c r="D46" s="22" t="s">
         <v>7</v>
@@ -4092,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C48" s="16"/>
       <c r="D48" s="3"/>
@@ -4146,7 +4164,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C52" s="16"/>
       <c r="D52" s="3"/>
@@ -4209,10 +4227,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C56" s="11">
         <v>1</v>
@@ -4238,7 +4256,7 @@
         <v>106</v>
       </c>
       <c r="C57" s="11">
-        <v>0.91964998512365381</v>
+        <v>0.90659390280881114</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -4261,7 +4279,7 @@
         <v>88</v>
       </c>
       <c r="C58" s="12">
-        <v>-1.51353683099332E-3</v>
+        <v>-1.4931786697317401E-3</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -4278,13 +4296,13 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="13">
-        <v>9.1406803346159078E-8</v>
+        <v>126</v>
+      </c>
+      <c r="C59" s="12">
+        <v>0</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -4307,7 +4325,7 @@
         <v>34</v>
       </c>
       <c r="C60" s="12">
-        <v>6.0754013722332099E-2</v>
+        <v>5.9409513565910815E-2</v>
       </c>
       <c r="D60" t="s">
         <v>35</v>
@@ -4330,7 +4348,7 @@
         <v>99</v>
       </c>
       <c r="C61" s="11">
-        <v>4.6646502651840436</v>
+        <v>4.5997084648075042</v>
       </c>
       <c r="D61" t="s">
         <v>29</v>
@@ -4353,7 +4371,7 @@
         <v>112</v>
       </c>
       <c r="C62" s="11">
-        <v>0.50722214107282404</v>
+        <v>0.59735221660353577</v>
       </c>
       <c r="D62" t="s">
         <v>29</v>
@@ -4373,7 +4391,7 @@
         <v>101</v>
       </c>
       <c r="C63" s="12">
-        <v>7.842128857001375E-2</v>
+        <v>7.4326007558944585E-2</v>
       </c>
       <c r="D63" s="22" t="s">
         <v>7</v>
@@ -4393,7 +4411,7 @@
         <v>110</v>
       </c>
       <c r="C64" s="23">
-        <v>2.0022743606470884E-4</v>
+        <v>1.0010620753264169E-4</v>
       </c>
       <c r="D64" s="22" t="s">
         <v>7</v>
@@ -4408,12 +4426,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>21</v>
       </c>
       <c r="C65" s="12">
-        <v>1.4556189599066783E-2</v>
+        <v>0</v>
       </c>
       <c r="D65" s="22" t="s">
         <v>7</v>
@@ -4425,6 +4443,1496 @@
         <v>102</v>
       </c>
       <c r="H65" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C67" s="16"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B68" s="6"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" s="16"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="9">
+        <v>1</v>
+      </c>
+      <c r="C70" s="16"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" t="s">
+        <v>129</v>
+      </c>
+      <c r="C71" s="16"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="16"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75" t="s">
+        <v>129</v>
+      </c>
+      <c r="C75" s="11">
+        <v>1</v>
+      </c>
+      <c r="D75" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" t="s">
+        <v>3</v>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H75" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>108</v>
+      </c>
+      <c r="B76" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" s="11">
+        <v>0.9036534629177585</v>
+      </c>
+      <c r="D76" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s">
+        <v>109</v>
+      </c>
+      <c r="H76" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B77" t="s">
+        <v>88</v>
+      </c>
+      <c r="C77" s="12">
+        <v>-1.48695855012261E-3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>109</v>
+      </c>
+      <c r="H77" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" t="s">
+        <v>126</v>
+      </c>
+      <c r="C78" s="12">
+        <v>0</v>
+      </c>
+      <c r="D78" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" t="s">
+        <v>3</v>
+      </c>
+      <c r="G78" t="s">
+        <v>109</v>
+      </c>
+      <c r="H78" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>33</v>
+      </c>
+      <c r="B79" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79" s="12">
+        <v>7.9660098771632923E-2</v>
+      </c>
+      <c r="D79" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" t="s">
+        <v>3</v>
+      </c>
+      <c r="G79" t="s">
+        <v>109</v>
+      </c>
+      <c r="H79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>99</v>
+      </c>
+      <c r="B80" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" s="11">
+        <v>5.0729694968067038</v>
+      </c>
+      <c r="D80" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" t="s">
+        <v>3</v>
+      </c>
+      <c r="G80" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>111</v>
+      </c>
+      <c r="B81" t="s">
+        <v>112</v>
+      </c>
+      <c r="C81" s="11">
+        <v>0</v>
+      </c>
+      <c r="D81" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" t="s">
+        <v>113</v>
+      </c>
+      <c r="G81" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H81" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="12">
+        <v>7.2978263473949576E-2</v>
+      </c>
+      <c r="D82" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82" t="s">
+        <v>102</v>
+      </c>
+      <c r="H82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>110</v>
+      </c>
+      <c r="C83" s="13">
+        <v>1.2448396935331403E-4</v>
+      </c>
+      <c r="D83" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" t="s">
+        <v>102</v>
+      </c>
+      <c r="H83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" s="12">
+        <v>0</v>
+      </c>
+      <c r="D84" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F84" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" t="s">
+        <v>102</v>
+      </c>
+      <c r="H84" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85" s="12">
+        <v>4.4878678307609801E-4</v>
+      </c>
+      <c r="D85" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F85" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" t="s">
+        <v>102</v>
+      </c>
+      <c r="H85" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C87" s="16"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B88" s="6"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B89" t="s">
+        <v>3</v>
+      </c>
+      <c r="C89" s="16"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" s="9">
+        <v>1</v>
+      </c>
+      <c r="C90" s="16"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>130</v>
+      </c>
+      <c r="C91" s="16"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="16"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>130</v>
+      </c>
+      <c r="B95" t="s">
+        <v>130</v>
+      </c>
+      <c r="C95" s="11">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" t="s">
+        <v>3</v>
+      </c>
+      <c r="G95" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H95" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>106</v>
+      </c>
+      <c r="B96" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" s="11">
+        <v>0.9036534629177585</v>
+      </c>
+      <c r="D96" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H96" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>89</v>
+      </c>
+      <c r="B97" t="s">
+        <v>88</v>
+      </c>
+      <c r="C97" s="12">
+        <v>-1.48695855012261E-3</v>
+      </c>
+      <c r="D97" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97" t="s">
+        <v>109</v>
+      </c>
+      <c r="H97" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>125</v>
+      </c>
+      <c r="B98" t="s">
+        <v>126</v>
+      </c>
+      <c r="C98" s="12">
+        <v>0</v>
+      </c>
+      <c r="D98" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" t="s">
+        <v>3</v>
+      </c>
+      <c r="G98" t="s">
+        <v>109</v>
+      </c>
+      <c r="H98" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" t="s">
+        <v>34</v>
+      </c>
+      <c r="C99" s="12">
+        <v>7.9660098771632923E-2</v>
+      </c>
+      <c r="D99" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" t="s">
+        <v>3</v>
+      </c>
+      <c r="G99" t="s">
+        <v>109</v>
+      </c>
+      <c r="H99" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>99</v>
+      </c>
+      <c r="C100" s="12">
+        <v>5.0729694968067038</v>
+      </c>
+      <c r="D100" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H100" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>111</v>
+      </c>
+      <c r="B101" t="s">
+        <v>112</v>
+      </c>
+      <c r="C101" s="12">
+        <v>0</v>
+      </c>
+      <c r="D101" t="s">
+        <v>29</v>
+      </c>
+      <c r="E101" t="s">
+        <v>113</v>
+      </c>
+      <c r="G101" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H101" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" s="12">
+        <v>7.2978263473949576E-2</v>
+      </c>
+      <c r="D102" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F102" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" t="s">
+        <v>102</v>
+      </c>
+      <c r="H102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>110</v>
+      </c>
+      <c r="C103" s="12">
+        <v>1.2448396935331403E-4</v>
+      </c>
+      <c r="D103" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F103" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103" t="s">
+        <v>102</v>
+      </c>
+      <c r="H103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>21</v>
+      </c>
+      <c r="C104" s="12">
+        <v>0</v>
+      </c>
+      <c r="D104" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F104" t="s">
+        <v>22</v>
+      </c>
+      <c r="G104" t="s">
+        <v>102</v>
+      </c>
+      <c r="H104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>86</v>
+      </c>
+      <c r="C105" s="12">
+        <v>4.4878678307609801E-4</v>
+      </c>
+      <c r="D105" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" t="s">
+        <v>22</v>
+      </c>
+      <c r="G105" t="s">
+        <v>102</v>
+      </c>
+      <c r="H105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="17"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C107" s="16"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B108" s="6"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" s="16"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B110" s="9">
+        <v>1</v>
+      </c>
+      <c r="C110" s="16"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" t="s">
+        <v>133</v>
+      </c>
+      <c r="C111" s="16"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="16"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" s="3"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>133</v>
+      </c>
+      <c r="B115" t="s">
+        <v>133</v>
+      </c>
+      <c r="C115" s="11">
+        <v>1</v>
+      </c>
+      <c r="D115" t="s">
+        <v>7</v>
+      </c>
+      <c r="E115" t="s">
+        <v>3</v>
+      </c>
+      <c r="G115" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H115" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>108</v>
+      </c>
+      <c r="B116" t="s">
+        <v>107</v>
+      </c>
+      <c r="C116" s="11">
+        <v>0.89440334956518253</v>
+      </c>
+      <c r="D116" t="s">
+        <v>7</v>
+      </c>
+      <c r="E116" t="s">
+        <v>15</v>
+      </c>
+      <c r="G116" t="s">
+        <v>109</v>
+      </c>
+      <c r="H116" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>89</v>
+      </c>
+      <c r="B117" t="s">
+        <v>88</v>
+      </c>
+      <c r="C117" s="12">
+        <v>-1.46247167513659E-3</v>
+      </c>
+      <c r="D117" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117" t="s">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>109</v>
+      </c>
+      <c r="H117" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>125</v>
+      </c>
+      <c r="B118" t="s">
+        <v>126</v>
+      </c>
+      <c r="C118" s="12">
+        <v>0</v>
+      </c>
+      <c r="D118" t="s">
+        <v>7</v>
+      </c>
+      <c r="E118" t="s">
+        <v>3</v>
+      </c>
+      <c r="G118" t="s">
+        <v>109</v>
+      </c>
+      <c r="H118" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" t="s">
+        <v>34</v>
+      </c>
+      <c r="C119" s="12">
+        <v>0.5473301234083312</v>
+      </c>
+      <c r="D119" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" t="s">
+        <v>3</v>
+      </c>
+      <c r="G119" t="s">
+        <v>109</v>
+      </c>
+      <c r="H119" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>99</v>
+      </c>
+      <c r="B120" t="s">
+        <v>99</v>
+      </c>
+      <c r="C120" s="11">
+        <v>12.942566664203866</v>
+      </c>
+      <c r="D120" t="s">
+        <v>29</v>
+      </c>
+      <c r="E120" t="s">
+        <v>3</v>
+      </c>
+      <c r="G120" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H120" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>111</v>
+      </c>
+      <c r="B121" t="s">
+        <v>112</v>
+      </c>
+      <c r="C121" s="11">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>29</v>
+      </c>
+      <c r="E121" t="s">
+        <v>113</v>
+      </c>
+      <c r="G121" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H121" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B122" t="s">
+        <v>36</v>
+      </c>
+      <c r="C122" s="11">
+        <v>0.28078564277733647</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G122" t="s">
+        <v>109</v>
+      </c>
+      <c r="H122" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>101</v>
+      </c>
+      <c r="C123" s="12">
+        <v>5.581483362661392</v>
+      </c>
+      <c r="D123" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F123" t="s">
+        <v>22</v>
+      </c>
+      <c r="G123" t="s">
+        <v>102</v>
+      </c>
+      <c r="H123" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C124" s="12">
+        <v>6.8140848616508071E-2</v>
+      </c>
+      <c r="D124" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F124" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124" t="s">
+        <v>102</v>
+      </c>
+      <c r="H124" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>135</v>
+      </c>
+      <c r="C125" s="12">
+        <v>1.4834478388868215E-3</v>
+      </c>
+      <c r="D125" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F125" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125" t="s">
+        <v>102</v>
+      </c>
+      <c r="H125" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="17"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C127" s="16"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B128" s="6"/>
+      <c r="C128" s="16"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B129" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="16"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B130" s="9">
+        <v>1</v>
+      </c>
+      <c r="C130" s="16"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" t="s">
+        <v>134</v>
+      </c>
+      <c r="C131" s="16"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B132" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="16"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B133" s="3"/>
+      <c r="C133" s="16"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G134" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>134</v>
+      </c>
+      <c r="C135" s="11">
+        <v>1</v>
+      </c>
+      <c r="D135" t="s">
+        <v>7</v>
+      </c>
+      <c r="E135" t="s">
+        <v>3</v>
+      </c>
+      <c r="G135" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H135" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>106</v>
+      </c>
+      <c r="B136" t="s">
+        <v>106</v>
+      </c>
+      <c r="C136" s="11">
+        <v>0.89440334956518253</v>
+      </c>
+      <c r="D136" t="s">
+        <v>7</v>
+      </c>
+      <c r="E136" t="s">
+        <v>3</v>
+      </c>
+      <c r="G136" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H136" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>89</v>
+      </c>
+      <c r="B137" t="s">
+        <v>88</v>
+      </c>
+      <c r="C137" s="12">
+        <v>-1.46247167513659E-3</v>
+      </c>
+      <c r="D137" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137" t="s">
+        <v>15</v>
+      </c>
+      <c r="G137" t="s">
+        <v>109</v>
+      </c>
+      <c r="H137" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>125</v>
+      </c>
+      <c r="B138" t="s">
+        <v>126</v>
+      </c>
+      <c r="C138" s="12">
+        <v>0</v>
+      </c>
+      <c r="D138" t="s">
+        <v>7</v>
+      </c>
+      <c r="E138" t="s">
+        <v>3</v>
+      </c>
+      <c r="G138" t="s">
+        <v>109</v>
+      </c>
+      <c r="H138" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>33</v>
+      </c>
+      <c r="B139" t="s">
+        <v>34</v>
+      </c>
+      <c r="C139" s="12">
+        <v>0.5473301234083312</v>
+      </c>
+      <c r="D139" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" t="s">
+        <v>3</v>
+      </c>
+      <c r="G139" t="s">
+        <v>109</v>
+      </c>
+      <c r="H139" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>99</v>
+      </c>
+      <c r="B140" t="s">
+        <v>99</v>
+      </c>
+      <c r="C140" s="11">
+        <v>12.942566664203866</v>
+      </c>
+      <c r="D140" t="s">
+        <v>29</v>
+      </c>
+      <c r="E140" t="s">
+        <v>3</v>
+      </c>
+      <c r="G140" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H140" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>111</v>
+      </c>
+      <c r="B141" t="s">
+        <v>112</v>
+      </c>
+      <c r="C141" s="11">
+        <v>0</v>
+      </c>
+      <c r="D141" t="s">
+        <v>29</v>
+      </c>
+      <c r="E141" t="s">
+        <v>113</v>
+      </c>
+      <c r="G141" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="H141" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B142" t="s">
+        <v>36</v>
+      </c>
+      <c r="C142" s="11">
+        <v>0.28078564277733647</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G142" t="s">
+        <v>109</v>
+      </c>
+      <c r="H142" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>101</v>
+      </c>
+      <c r="C143" s="12">
+        <v>5.581483362661392</v>
+      </c>
+      <c r="D143" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F143" t="s">
+        <v>22</v>
+      </c>
+      <c r="G143" t="s">
+        <v>102</v>
+      </c>
+      <c r="H143" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>21</v>
+      </c>
+      <c r="C144" s="12">
+        <v>6.8140848616508071E-2</v>
+      </c>
+      <c r="D144" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F144" t="s">
+        <v>22</v>
+      </c>
+      <c r="G144" t="s">
+        <v>102</v>
+      </c>
+      <c r="H144" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>135</v>
+      </c>
+      <c r="C145" s="12">
+        <v>1.4834478388868215E-3</v>
+      </c>
+      <c r="D145" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F145" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145" t="s">
+        <v>102</v>
+      </c>
+      <c r="H145" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4454,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="3"/>
@@ -4508,7 +6016,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="3"/>
@@ -4571,10 +6079,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="11">
         <v>1</v>
@@ -4599,8 +6107,8 @@
       <c r="B10" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="12">
-        <v>6.5856585494280195E-2</v>
+      <c r="C10" s="24">
+        <v>6.5856585494280209E-2</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4622,7 +6130,7 @@
       <c r="B11" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="24">
         <v>3.0874916157909655E-3</v>
       </c>
       <c r="D11" t="s">
@@ -4645,7 +6153,7 @@
       <c r="B12" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="24">
         <v>1.9300000000000001E-3</v>
       </c>
       <c r="D12" t="s">
@@ -4668,7 +6176,7 @@
       <c r="B13" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="24">
         <v>-5.7016971421526401E-4</v>
       </c>
       <c r="D13" t="s">
@@ -4686,13 +6194,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="13">
-        <v>2.5650000000000022E-9</v>
+        <v>127</v>
+      </c>
+      <c r="C14" s="24">
+        <v>0</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4714,7 +6222,7 @@
       <c r="B15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="24">
         <v>8.8525186072921841E-2</v>
       </c>
       <c r="D15" t="s">
@@ -4853,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="3"/>
@@ -4907,7 +6415,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="3"/>
@@ -4970,10 +6478,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30" s="11">
         <v>1</v>
@@ -4998,7 +6506,7 @@
       <c r="B31" t="s">
         <v>104</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="24">
         <v>6.5856585494280209E-2</v>
       </c>
       <c r="D31" t="s">
@@ -5021,7 +6529,7 @@
       <c r="B32" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="24">
         <v>3.0874916157909655E-3</v>
       </c>
       <c r="D32" t="s">
@@ -5044,7 +6552,7 @@
       <c r="B33" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="24">
         <v>1.9300000000000001E-3</v>
       </c>
       <c r="D33" t="s">
@@ -5067,7 +6575,7 @@
       <c r="B34" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="24">
         <v>-5.7016971421526401E-4</v>
       </c>
       <c r="D34" t="s">
@@ -5085,13 +6593,13 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>129</v>
-      </c>
-      <c r="C35" s="13">
-        <v>2.5650000000000022E-9</v>
+        <v>127</v>
+      </c>
+      <c r="C35" s="24">
+        <v>0</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -5113,7 +6621,7 @@
       <c r="B36" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="24">
         <v>8.8525186072921841E-2</v>
       </c>
       <c r="D36" t="s">

--- a/data/inventories_ei310.xlsx
+++ b/data/inventories_ei310.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B4DC5D-D9D3-4837-BA64-23010486F629}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AB029A-7629-42DD-BE7D-9833B9E5FCD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="2" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14400" windowHeight="4110" activeTab="4" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="hydrogen" sheetId="14" r:id="rId1"/>
     <sheet name="ammonia" sheetId="15" r:id="rId2"/>
     <sheet name="nitrous_oxide" sheetId="25" r:id="rId3"/>
     <sheet name="hydrogen_peroxide" sheetId="26" r:id="rId4"/>
+    <sheet name="phenol" sheetId="27" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="141">
   <si>
     <t>Activity</t>
   </si>
@@ -436,6 +437,21 @@
   </si>
   <si>
     <t>Nitric acid</t>
+  </si>
+  <si>
+    <t>phenol production, nitrous oxide, fossil</t>
+  </si>
+  <si>
+    <t>Benzene</t>
+  </si>
+  <si>
+    <t>phenol production, nitrous oxide, green</t>
+  </si>
+  <si>
+    <t>phenol production, hydrogen peroxide, fossil</t>
+  </si>
+  <si>
+    <t>phenol production, hydrogen peroxide, green</t>
   </si>
 </sst>
 </file>
@@ -6749,4 +6765,1252 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150773DC-8801-4506-8832-5BE54A26FACF}">
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="9">
+        <v>1</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="24">
+        <v>0.82850000000000001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="24">
+        <v>0.4753</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="24">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0.97905439999999999</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="11">
+        <v>12.783581</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="11">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="13">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="11">
+        <v>0.30220000000000002</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="9">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="11">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="24">
+        <v>0.82850000000000001</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="24">
+        <v>0.4753</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="24">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="11">
+        <v>0.97905439999999999</v>
+      </c>
+      <c r="D31" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="11">
+        <v>12.783581</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="11">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="13">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="11">
+        <v>0.30220000000000002</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="16"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="9">
+        <v>1</v>
+      </c>
+      <c r="C40" s="16"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="16"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" s="11">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>120</v>
+      </c>
+      <c r="B46" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="24">
+        <v>0.92220000000000002</v>
+      </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s">
+        <v>109</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="24">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" t="s">
+        <v>105</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="24">
+        <v>0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" t="s">
+        <v>109</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="11">
+        <v>4.9474215120689138</v>
+      </c>
+      <c r="D49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="11">
+        <v>6.9231678675119195</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>109</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="13">
+        <v>-2.7E-4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" s="16"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" s="6"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="16"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="9">
+        <v>1</v>
+      </c>
+      <c r="C56" s="16"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" s="16"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="16"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="11">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
+        <v>3</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H61" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>120</v>
+      </c>
+      <c r="B62" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="24">
+        <v>0.92220000000000002</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s">
+        <v>109</v>
+      </c>
+      <c r="H62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" s="24">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s">
+        <v>3</v>
+      </c>
+      <c r="G63" t="s">
+        <v>105</v>
+      </c>
+      <c r="H63" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" s="24">
+        <v>0</v>
+      </c>
+      <c r="D64" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" t="s">
+        <v>3</v>
+      </c>
+      <c r="G64" t="s">
+        <v>109</v>
+      </c>
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>99</v>
+      </c>
+      <c r="B65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" s="11">
+        <v>4.9474215120689138</v>
+      </c>
+      <c r="D65" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" t="s">
+        <v>3</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H65" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" s="11">
+        <v>6.9231678675119195</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s">
+        <v>109</v>
+      </c>
+      <c r="H66" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>89</v>
+      </c>
+      <c r="B67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="13">
+        <v>-2.7E-4</v>
+      </c>
+      <c r="D67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s">
+        <v>109</v>
+      </c>
+      <c r="H67" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>